--- a/data/trans_camb/IP12-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP12-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 9,74</t>
+          <t>-2,72; 9,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 2,96</t>
+          <t>-7,94; 3,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 4,54</t>
+          <t>-6,49; 4,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 3,48</t>
+          <t>-5,95; 3,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 1,71</t>
+          <t>-7,49; 2,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 3,51</t>
+          <t>-6,23; 3,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 5,16</t>
+          <t>-2,77; 5,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 0,94</t>
+          <t>-5,98; 1,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 2,35</t>
+          <t>-5,31; 2,54</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-25,81; 161,34</t>
+          <t>-23,82; 160,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-65,29; 52,52</t>
+          <t>-67,31; 61,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-58,91; 73,97</t>
+          <t>-59,36; 83,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-59,22; 72,3</t>
+          <t>-58,03; 74,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-75,67; 44,78</t>
+          <t>-71,61; 45,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-64,03; 65,46</t>
+          <t>-62,34; 78,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-30,73; 80,16</t>
+          <t>-28,55; 89,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-58,17; 17,12</t>
+          <t>-58,83; 19,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-50,59; 37,06</t>
+          <t>-50,55; 40,04</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 7,43</t>
+          <t>-0,95; 7,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 7,55</t>
+          <t>-0,95; 7,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 5,09</t>
+          <t>-3,19; 5,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 2,66</t>
+          <t>-5,44; 2,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 3,33</t>
+          <t>-4,7; 3,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 3,0</t>
+          <t>-5,14; 2,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 3,36</t>
+          <t>-2,4; 3,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 4,24</t>
+          <t>-1,73; 4,18</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 2,78</t>
+          <t>-3,06; 2,57</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,2; 189,69</t>
+          <t>-13,68; 154,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 183,7</t>
+          <t>-14,04; 177,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-41,73; 111,62</t>
+          <t>-42,12; 118,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-56,04; 51,15</t>
+          <t>-54,87; 47,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-49,71; 55,95</t>
+          <t>-47,6; 56,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-50,24; 54,64</t>
+          <t>-52,98; 42,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-28,26; 56,67</t>
+          <t>-28,76; 60,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-19,65; 72,14</t>
+          <t>-20,4; 73,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-33,25; 48,54</t>
+          <t>-37,43; 48,08</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 1,66</t>
+          <t>-7,95; 1,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 3,56</t>
+          <t>-7,46; 3,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 3,5</t>
+          <t>-6,9; 3,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 10,38</t>
+          <t>0,78; 10,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 9,03</t>
+          <t>-0,82; 8,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 8,56</t>
+          <t>-1,54; 8,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 4,49</t>
+          <t>-2,43; 4,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 4,66</t>
+          <t>-2,04; 4,88</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 4,57</t>
+          <t>-3,05; 4,64</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-66,94; 26,05</t>
+          <t>-67,17; 23,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-51,93; 55,97</t>
+          <t>-57,6; 50,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-59,67; 49,92</t>
+          <t>-58,75; 52,99</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,15; 299,69</t>
+          <t>4,13; 305,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-12,95; 241,7</t>
+          <t>-15,21; 251,02</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-22,08; 262,34</t>
+          <t>-22,93; 240,18</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-27,31; 76,94</t>
+          <t>-27,7; 84,16</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-22,61; 83,35</t>
+          <t>-25,13; 84,84</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-32,42; 78,96</t>
+          <t>-32,34; 79,35</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,3; 7,52</t>
+          <t>0,43; 7,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 7,24</t>
+          <t>-0,03; 7,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 6,62</t>
+          <t>-0,66; 6,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,86; 9,45</t>
+          <t>0,86; 9,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 2,73</t>
+          <t>-4,0; 2,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,29; 8,85</t>
+          <t>-0,13; 9,11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,91; 7,42</t>
+          <t>1,67; 7,48</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 4,11</t>
+          <t>-0,86; 3,96</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,8; 6,58</t>
+          <t>1,01; 6,8</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 391,41</t>
+          <t>0,15; 384,61</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 418,56</t>
+          <t>-12,86; 388,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-20,61; 387,87</t>
+          <t>-25,29; 336,55</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,58; 275,4</t>
+          <t>11,08; 286,95</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-59,8; 87,01</t>
+          <t>-58,31; 93,36</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 252,06</t>
+          <t>-4,02; 250,3</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,45; 238,33</t>
+          <t>28,13; 247,42</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-18,88; 129,11</t>
+          <t>-17,93; 128,01</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13,27; 201,64</t>
+          <t>15,13; 216,92</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 4,46</t>
+          <t>-0,31; 4,41</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 3,77</t>
+          <t>-0,9; 3,59</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 3,31</t>
+          <t>-1,53; 3,14</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 4,17</t>
+          <t>-0,51; 3,95</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 1,97</t>
+          <t>-2,04; 2,14</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 3,56</t>
+          <t>-1,06; 3,86</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,88</t>
+          <t>0,36; 3,67</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 2,3</t>
+          <t>-0,68; 2,37</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 2,66</t>
+          <t>-0,58; 2,63</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 80,85</t>
+          <t>-5,0; 81,05</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-11,39; 69,18</t>
+          <t>-13,17; 66,76</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-19,53; 59,9</t>
+          <t>-21,57; 57,45</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 71,89</t>
+          <t>-7,28; 69,01</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-28,71; 34,06</t>
+          <t>-26,39; 38,65</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-16,31; 62,95</t>
+          <t>-13,37; 67,73</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,62; 67,37</t>
+          <t>5,84; 64,64</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-13,13; 41,49</t>
+          <t>-9,77; 42,04</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 47,48</t>
+          <t>-8,73; 44,17</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP12-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP12-Habitat-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolores o síntomas</t>
+          <t>Menores que en las últimas 2 semanas limitaron su actividad por dolores o síntomas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 9,69</t>
+          <t>-2,69; 9,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 3,5</t>
+          <t>-7,68; 3,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 4,54</t>
+          <t>-6,94; 4,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 3,84</t>
+          <t>-5,97; 3,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 2,1</t>
+          <t>-7,91; 1,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 3,78</t>
+          <t>-6,02; 4,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 5,3</t>
+          <t>-2,87; 5,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 1,11</t>
+          <t>-6,15; 1,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 2,54</t>
+          <t>-4,99; 2,48</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-23,82; 160,32</t>
+          <t>-23,47; 162,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-67,31; 61,54</t>
+          <t>-67,12; 63,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-59,36; 83,25</t>
+          <t>-60,04; 75,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-58,03; 74,8</t>
+          <t>-57,19; 77,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-71,61; 45,99</t>
+          <t>-75,2; 38,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-62,34; 78,36</t>
+          <t>-59,76; 82,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-28,55; 89,15</t>
+          <t>-29,5; 84,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-58,83; 19,99</t>
+          <t>-61,46; 18,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-50,55; 40,04</t>
+          <t>-50,55; 38,31</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 7,3</t>
+          <t>-0,83; 7,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 7,61</t>
+          <t>-0,18; 7,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 5,13</t>
+          <t>-2,87; 5,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 2,53</t>
+          <t>-5,77; 2,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 3,1</t>
+          <t>-4,89; 3,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 2,3</t>
+          <t>-5,27; 2,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 3,47</t>
+          <t>-2,03; 3,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 4,18</t>
+          <t>-1,3; 4,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 2,57</t>
+          <t>-2,66; 2,84</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,68; 154,23</t>
+          <t>-13,06; 168,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-14,04; 177,08</t>
+          <t>-10,22; 170,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-42,12; 118,41</t>
+          <t>-37,0; 118,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-54,87; 47,56</t>
+          <t>-57,04; 45,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-47,6; 56,07</t>
+          <t>-50,67; 66,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-52,98; 42,79</t>
+          <t>-52,74; 50,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-28,76; 60,17</t>
+          <t>-25,43; 60,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-20,4; 73,33</t>
+          <t>-16,97; 76,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-37,43; 48,08</t>
+          <t>-32,47; 46,79</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 1,34</t>
+          <t>-8,66; 1,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 3,21</t>
+          <t>-6,53; 4,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 3,54</t>
+          <t>-7,21; 3,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,78; 10,16</t>
+          <t>0,36; 10,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 8,64</t>
+          <t>-0,43; 9,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 8,39</t>
+          <t>-1,8; 8,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 4,83</t>
+          <t>-2,25; 4,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 4,88</t>
+          <t>-2,1; 5,02</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 4,64</t>
+          <t>-2,93; 5,11</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-67,17; 23,89</t>
+          <t>-68,57; 26,78</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-57,6; 50,56</t>
+          <t>-54,15; 74,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-58,75; 52,99</t>
+          <t>-58,75; 59,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,13; 305,14</t>
+          <t>-4,39; 282,04</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-15,21; 251,02</t>
+          <t>-8,16; 256,39</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-22,93; 240,18</t>
+          <t>-28,61; 234,11</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-27,7; 84,16</t>
+          <t>-26,5; 80,87</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-25,13; 84,84</t>
+          <t>-24,22; 89,85</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-32,34; 79,35</t>
+          <t>-34,01; 91,43</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 7,81</t>
+          <t>0,86; 8,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 7,69</t>
+          <t>0,2; 7,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 6,44</t>
+          <t>-0,85; 6,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,86; 9,59</t>
+          <t>0,76; 9,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 2,98</t>
+          <t>-3,95; 2,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 9,11</t>
+          <t>-0,05; 9,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,67; 7,48</t>
+          <t>1,78; 7,62</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 3,96</t>
+          <t>-1,0; 3,91</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,01; 6,8</t>
+          <t>0,84; 6,64</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,15; 384,61</t>
+          <t>12,57; 492,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-12,86; 388,48</t>
+          <t>-4,61; 398,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-25,29; 336,55</t>
+          <t>-23,05; 351,1</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11,08; 286,95</t>
+          <t>5,42; 294,07</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-58,31; 93,36</t>
+          <t>-58,7; 95,98</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 250,3</t>
+          <t>-3,37; 258,55</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,13; 247,42</t>
+          <t>28,22; 250,64</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-17,93; 128,01</t>
+          <t>-19,92; 126,49</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>15,13; 216,92</t>
+          <t>10,7; 213,92</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 4,41</t>
+          <t>-0,17; 4,56</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 3,59</t>
+          <t>-0,62; 3,81</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 3,14</t>
+          <t>-1,82; 2,67</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 3,95</t>
+          <t>-0,38; 4,06</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 2,14</t>
+          <t>-2,21; 2,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 3,86</t>
+          <t>-0,89; 3,65</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,67</t>
+          <t>0,44; 3,63</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 2,37</t>
+          <t>-0,8; 2,22</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 2,63</t>
+          <t>-0,74; 2,56</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 81,05</t>
+          <t>-2,67; 84,31</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-13,17; 66,76</t>
+          <t>-10,06; 71,9</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-21,57; 57,45</t>
+          <t>-23,69; 48,84</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 69,01</t>
+          <t>-5,66; 72,04</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-26,39; 38,65</t>
+          <t>-28,86; 35,74</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 67,73</t>
+          <t>-11,73; 68,18</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,84; 64,64</t>
+          <t>6,13; 61,11</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-9,77; 42,04</t>
+          <t>-10,75; 38,64</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-8,73; 44,17</t>
+          <t>-10,59; 43,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP12-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP12-Habitat-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-1,1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-2,89</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-1,05</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>3,48</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-2,19</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-1,28</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-1,1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-2,89</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,39</t>
+          <t>-1,31</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,36</t>
+          <t>-1,16</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 9,25</t>
+          <t>-5,95; 3,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,68; 3,78</t>
+          <t>-8,07; 1,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 4,23</t>
+          <t>-6,22; 4,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 3,81</t>
+          <t>-3,18; 9,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 1,64</t>
+          <t>-7,4; 2,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 4,18</t>
+          <t>-7,18; 4,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 5,22</t>
+          <t>-2,92; 5,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 1,12</t>
+          <t>-6,17; 0,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 2,48</t>
+          <t>-5,0; 2,63</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-14,27%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-37,57%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-13,7%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>39,4%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-24,8%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-14,46%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-14,27%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-37,57%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-18,1%</t>
+          <t>-14,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-16,55%</t>
+          <t>-14,13%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-23,47; 162,32</t>
+          <t>-59,22; 72,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-67,12; 63,4</t>
+          <t>-75,67; 44,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-60,04; 75,88</t>
+          <t>-61,69; 74,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-57,19; 77,65</t>
+          <t>-25,81; 161,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-75,2; 38,56</t>
+          <t>-65,29; 52,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-59,76; 82,14</t>
+          <t>-59,59; 72,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-29,5; 84,13</t>
+          <t>-30,73; 80,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-61,46; 18,16</t>
+          <t>-58,17; 17,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-50,55; 38,31</t>
+          <t>-48,87; 41,56</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-1,62</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,72</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-1,06</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>3,1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>3,61</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,94</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,62</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,72</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-1,18</t>
+          <t>0,7</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,19</t>
+          <t>-0,22</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 7,58</t>
+          <t>-5,73; 2,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 7,83</t>
+          <t>-4,74; 3,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 5,08</t>
+          <t>-5,09; 3,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 2,43</t>
+          <t>-0,73; 7,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 3,55</t>
+          <t>-0,42; 7,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 2,8</t>
+          <t>-3,54; 4,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 3,42</t>
+          <t>-2,41; 3,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 4,2</t>
+          <t>-1,69; 4,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 2,84</t>
+          <t>-2,92; 2,74</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-20,46%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-9,11%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-13,36%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>50,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>58,33%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>15,12%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-20,46%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-9,11%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-14,89%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-2,62%</t>
+          <t>-3,05%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,06; 168,77</t>
+          <t>-56,04; 51,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-10,22; 170,46</t>
+          <t>-49,71; 55,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-37,0; 118,72</t>
+          <t>-50,54; 56,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-57,04; 45,14</t>
+          <t>-10,2; 189,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-50,67; 66,15</t>
+          <t>-7,07; 183,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-52,74; 50,54</t>
+          <t>-43,16; 111,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-25,43; 60,17</t>
+          <t>-28,26; 56,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-16,97; 76,61</t>
+          <t>-19,65; 72,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-32,47; 46,79</t>
+          <t>-33,35; 49,2</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>5,34</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>4,03</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3,67</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-3,15</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-1,4</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-1,56</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5,34</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>4,03</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,15</t>
+          <t>0,17</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>1,99</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,66; 1,49</t>
+          <t>0,86; 10,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 4,1</t>
+          <t>-0,49; 9,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 3,66</t>
+          <t>-1,18; 9,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 10,07</t>
+          <t>-8,07; 1,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 9,1</t>
+          <t>-6,29; 3,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 8,92</t>
+          <t>-5,51; 5,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 4,71</t>
+          <t>-2,34; 4,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 5,02</t>
+          <t>-2,13; 4,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 5,11</t>
+          <t>-1,88; 5,9</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>96,62%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>72,93%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>66,28%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-34,22%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-15,16%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-16,9%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>96,62%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>72,93%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>27,25%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-68,57; 26,78</t>
+          <t>9,15; 299,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-54,15; 74,57</t>
+          <t>-12,95; 241,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-58,75; 59,34</t>
+          <t>-19,67; 285,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 282,04</t>
+          <t>-66,94; 26,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 256,39</t>
+          <t>-51,93; 55,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-28,61; 234,11</t>
+          <t>-43,87; 78,87</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-26,5; 80,87</t>
+          <t>-27,31; 76,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-24,22; 89,85</t>
+          <t>-22,61; 83,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-34,01; 91,43</t>
+          <t>-20,8; 97,99</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5,08</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,56</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3,95</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>4,12</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>3,67</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2,87</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5,08</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,56</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,3</t>
+          <t>2,82</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,65</t>
+          <t>3,4</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,86; 8,04</t>
+          <t>0,86; 9,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,2; 7,29</t>
+          <t>-3,97; 2,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 6,45</t>
+          <t>-0,18; 8,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,76; 9,91</t>
+          <t>0,3; 7,52</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 2,89</t>
+          <t>-0,08; 7,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 9,0</t>
+          <t>-0,68; 6,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,78; 7,62</t>
+          <t>1,91; 7,42</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 3,91</t>
+          <t>-0,89; 4,11</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,84; 6,64</t>
+          <t>0,6; 6,29</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>100,55%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-11,06%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>78,28%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>126,13%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>112,11%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>87,78%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>100,55%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-11,06%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>81,77%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>12,57; 492,9</t>
+          <t>8,58; 275,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 398,67</t>
+          <t>-59,8; 87,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-23,05; 351,1</t>
+          <t>-6,66; 250,39</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,42; 294,07</t>
+          <t>-5,4; 391,41</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-58,7; 95,98</t>
+          <t>-6,34; 418,56</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 258,55</t>
+          <t>-19,41; 393,74</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,22; 250,64</t>
+          <t>29,45; 238,33</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-19,92; 126,49</t>
+          <t>-18,88; 129,11</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10,7; 213,92</t>
+          <t>9,09; 191,42</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1,88</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,05</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1,35</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>2,17</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1,48</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0,66</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1,88</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-0,05</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>0,98</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>1,17</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 4,56</t>
+          <t>-0,27; 4,17</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 3,81</t>
+          <t>-2,16; 1,97</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 2,67</t>
+          <t>-1,17; 3,76</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 4,06</t>
+          <t>-0,06; 4,46</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 2,03</t>
+          <t>-0,88; 3,77</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 3,65</t>
+          <t>-1,16; 3,56</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,63</t>
+          <t>0,61; 3,88</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 2,22</t>
+          <t>-0,95; 2,3</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 2,56</t>
+          <t>-0,33; 3,06</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>28,63%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-0,74%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>20,55%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>33,72%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>22,9%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>10,28%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>28,63%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-0,74%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>18,04%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 84,31</t>
+          <t>-4,72; 71,89</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-10,06; 71,9</t>
+          <t>-28,71; 34,06</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-23,69; 48,84</t>
+          <t>-15,48; 66,4</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 72,04</t>
+          <t>-1,3; 80,85</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-28,86; 35,74</t>
+          <t>-11,39; 69,18</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-11,73; 68,18</t>
+          <t>-15,97; 69,01</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,13; 61,11</t>
+          <t>7,62; 67,37</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-10,75; 38,64</t>
+          <t>-13,13; 41,49</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 43,58</t>
+          <t>-5,75; 52,29</t>
         </is>
       </c>
     </row>
